--- a/Rate card J&T.xlsx
+++ b/Rate card J&T.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\Studio rateoil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2D7890-85F7-4098-9762-87183E40BACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC2BEF6-FCDD-4073-8161-A2FF386D0422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E98A5B8D-D3F7-412D-9177-88D88937ED16}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E98A5B8D-D3F7-412D-9177-88D88937ED16}"/>
   </bookViews>
   <sheets>
     <sheet name="ราคารับ" sheetId="1" r:id="rId1"/>
     <sheet name="data J&amp;T" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1011,22 +1012,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1035,19 +1033,22 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1487,144 +1488,144 @@
       <c r="AH10" s="12"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="17" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="17" t="s">
+      <c r="K11" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="15" t="s">
+      <c r="N11" s="17" t="s">
         <v>10</v>
       </c>
       <c r="O11" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="P11" s="15" t="s">
+      <c r="P11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="Q11" s="14" t="s">
+      <c r="Q11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="R11" s="15" t="s">
+      <c r="R11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="S11" s="20" t="s">
+      <c r="S11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="T11" s="21" t="s">
+      <c r="T11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="U11" s="22" t="s">
+      <c r="U11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="V11" s="21" t="s">
+      <c r="V11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="W11" s="23" t="s">
+      <c r="W11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="X11" s="21" t="s">
+      <c r="X11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="Y11" s="24" t="s">
+      <c r="Y11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="Z11" s="21" t="s">
+      <c r="Z11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AA11" s="25" t="s">
+      <c r="AA11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="AB11" s="21" t="s">
+      <c r="AB11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AC11" s="19" t="s">
+      <c r="AC11" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="AD11" s="21" t="s">
+      <c r="AD11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="AE11" s="23" t="s">
+      <c r="AE11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="AF11" s="21" t="s">
+      <c r="AF11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AG11" s="24" t="s">
+      <c r="AG11" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AH11" s="21" t="s">
+      <c r="AH11" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="15"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="16"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="15"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="17"/>
       <c r="O12" s="16"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="21"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="21"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="21"/>
-      <c r="AE12" s="23"/>
-      <c r="AF12" s="21"/>
-      <c r="AG12" s="24"/>
-      <c r="AH12" s="21"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="15"/>
+      <c r="AH12" s="13"/>
     </row>
     <row r="13" spans="1:36" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -2490,6 +2491,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="F9:AH10"/>
     <mergeCell ref="AD11:AD12"/>
     <mergeCell ref="AE11:AE12"/>
@@ -2506,25 +2526,6 @@
     <mergeCell ref="V11:V12"/>
     <mergeCell ref="W11:W12"/>
     <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2609,138 +2610,138 @@
       <c r="AF2" s="12"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="17" t="s">
         <v>10</v>
       </c>
       <c r="M3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="O3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="R3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="22" t="s">
+      <c r="S3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="21" t="s">
+      <c r="T3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="23" t="s">
+      <c r="U3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="V3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="24" t="s">
+      <c r="W3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="X3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="25" t="s">
+      <c r="Y3" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="Z3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="19" t="s">
+      <c r="AA3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="21" t="s">
+      <c r="AB3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="AC3" s="23" t="s">
+      <c r="AC3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="AD3" s="21" t="s">
+      <c r="AD3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AE3" s="24" t="s">
+      <c r="AE3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AF3" s="21" t="s">
+      <c r="AF3" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="15"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="16"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="15"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="17"/>
       <c r="M4" s="16"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="21"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="18"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="13"/>
     </row>
-    <row r="5" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>268</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>269</v>
       </c>
@@ -2936,7 +2937,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>270</v>
       </c>
@@ -3034,7 +3035,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>270</v>
       </c>
@@ -3132,7 +3133,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>155</v>
       </c>
@@ -3230,7 +3231,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>271</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>272</v>
       </c>
@@ -3426,7 +3427,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>273</v>
       </c>
@@ -3526,30 +3527,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="D1:AF2"/>
     <mergeCell ref="A3:A4"/>
@@ -3559,7 +3536,40 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D91251AA-6FB8-4D3B-95AA-ABDE9CE419F7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>